--- a/Hand_edited_log/6/StudentsSolution.xlsx
+++ b/Hand_edited_log/6/StudentsSolution.xlsx
@@ -40,121 +40,163 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
+    <x:t>AnhDHHE186569</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BangTCHE180772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
     <x:t>baonvthe180736</x:t>
   </x:si>
   <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
+    <x:t>4</x:t>
   </x:si>
   <x:si>
     <x:t>datdthe181502</x:t>
   </x:si>
   <x:si>
-    <x:t>3</x:t>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtahe182204</x:t>
   </x:si>
   <x:si>
     <x:t>duongnthe181806</x:t>
   </x:si>
   <x:si>
-    <x:t>4</x:t>
+    <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>duyndhe180130</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
+    <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>hungpvhe180243</x:t>
   </x:si>
   <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huylphe170368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
     <x:t>manhndhe186737</x:t>
   </x:si>
   <x:si>
-    <x:t>7</x:t>
+    <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t>namlxhhe186138</x:t>
   </x:si>
   <x:si>
-    <x:t>8</x:t>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>namnhmhe171148</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
+    <x:t>13</x:t>
   </x:si>
   <x:si>
     <x:t>phonglhhe186973</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phongnhhe181714</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PhuDKHE186439</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>quannnhe176871</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quitdhe176583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>quyendvhe180585</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
+    <x:t>19</x:t>
   </x:si>
   <x:si>
     <x:t>sonddthe173082</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
+    <x:t>20</x:t>
   </x:si>
   <x:si>
     <x:t>tainvhe187366</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
+    <x:t>21</x:t>
   </x:si>
   <x:si>
     <x:t>thainthe141476</x:t>
   </x:si>
   <x:si>
-    <x:t>15</x:t>
+    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>tientvhs176262</x:t>
   </x:si>
   <x:si>
-    <x:t>16</x:t>
+    <x:t>23</x:t>
   </x:si>
   <x:si>
     <x:t>tuannnhe151195</x:t>
   </x:si>
   <x:si>
-    <x:t>17</x:t>
+    <x:t>24</x:t>
   </x:si>
   <x:si>
     <x:t>tunahe186804</x:t>
   </x:si>
   <x:si>
-    <x:t>18</x:t>
+    <x:t>25</x:t>
   </x:si>
   <x:si>
     <x:t>Tungnxhe176893</x:t>
   </x:si>
   <x:si>
-    <x:t>19</x:t>
+    <x:t>26</x:t>
   </x:si>
   <x:si>
     <x:t>vietthhe186188</x:t>
@@ -528,7 +570,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G20"/>
+  <x:dimension ref="A1:G27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.424911" style="0" customWidth="1"/>
@@ -1000,6 +1042,167 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
+    <x:row r="21" spans="1:7">
+      <x:c r="A21" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:7">
+      <x:c r="A22" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:7">
+      <x:c r="A23" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:7">
+      <x:c r="A24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7">
+      <x:c r="A25" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:7">
+      <x:c r="A26" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:7">
+      <x:c r="A27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
